--- a/Hálózat tesztelése shéma.xlsx
+++ b/Hálózat tesztelése shéma.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\OneDrive\Asztali gép\Vizsgaremek\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC4F003-6840-4379-B287-98CE797E5BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF31F9D0-AA27-412E-9CCD-285AF2942F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Munkalap1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="SZUM">Munkalap1!$J$20</definedName>
+  </definedNames>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="341">
   <si>
     <t>Tesztelt szoftver</t>
   </si>
@@ -410,79 +413,640 @@
     <t>-</t>
   </si>
   <si>
-    <t>Router14-Router12 - Levelezés</t>
-  </si>
-  <si>
-    <t>Router14-Router13 - Levelezés</t>
-  </si>
-  <si>
-    <t>Router14-Router11 - Levelezés</t>
-  </si>
-  <si>
-    <t>Router14-Router3 - Levelezés</t>
-  </si>
-  <si>
-    <t>Router14-PC12 - Levelezés</t>
-  </si>
-  <si>
-    <t>Csak akkor ha nicsen be IP címezve és összekötve a két router</t>
-  </si>
-  <si>
-    <t>Rányomtam a levélre majd rákatintottam a Router14re majd a Router12re</t>
-  </si>
-  <si>
-    <t>Rányomtam a levélre majd rákatintottam a Router14ra majd a Router13ra</t>
-  </si>
-  <si>
-    <t>Rányomtam a levélre majd rákatintottam a Router14re majd a Router11re</t>
-  </si>
-  <si>
-    <t>Rányomtam a levélre majd rákatintottam a Router14re majd a Router3ra</t>
-  </si>
-  <si>
-    <t>Rányomtam a levélre majd rákatintottam a Router14re majd a PC12re</t>
-  </si>
-  <si>
     <t>Sikeres tesztelést várunk</t>
   </si>
   <si>
     <t>Sikeres lett</t>
   </si>
   <si>
-    <t>Csak akkor ha nicsen be IP címezve és összekötve a két eszköz</t>
-  </si>
-  <si>
-    <t>Csak akkor ha nicsen be IP címezve és összekötve eszköz</t>
-  </si>
-  <si>
-    <t>PC12-PC0 - Levelezés</t>
-  </si>
-  <si>
-    <t>PC12-PC1 - Levelezés</t>
-  </si>
-  <si>
-    <t>PC12-PC2 - Levelezés</t>
-  </si>
-  <si>
-    <t>PC12-PC3 - Levelezés</t>
-  </si>
-  <si>
-    <t>PC12-PC4 - Levelezés</t>
-  </si>
-  <si>
-    <t>Rányomtam a levélre majd rákatintottam a PC12 majd a PC0ra</t>
-  </si>
-  <si>
-    <t>Rányomtam a levélre majd rákatintottam a PC12 majd a PC1re</t>
-  </si>
-  <si>
-    <t>Rányomtam a levélre majd rákatintottam a PC12 majd a PC2re</t>
-  </si>
-  <si>
-    <t>Rányomtam a levélre majd rákatintottam a PC12 majd a PC3ra</t>
-  </si>
-  <si>
-    <t>Rányomtam a levélre majd rákatintottam a PC12 majd a PC4re</t>
+    <t>Összekötő Router-Debrecen Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Összekötő Router-Budapest Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Összekötő Router-Budapest Szerver Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Összekötő Router-Budapest Szerver PC - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver PC-Debrecen PC1 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver PC-Debrecen PC2 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver PC-Debrecen PC3 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver PC-Debrecen PC4 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver PC-Debrecen PC5 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver PC-Debrecen PC6 - Levelezés</t>
+  </si>
+  <si>
+    <t>Összekötő Router-Szeged Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Összekötő Router-re majd a Budapest Szerver Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Összekötő Router-re majd a Budapest Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Összekötő Router-re majd a Debrecen Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Összekötő Router-re majd a Szeged router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver PC-re majd a Debrecen PC1-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver PC-re majd a Debrecen PC2-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver PC-re majd a Debrecen PC3-ra</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver PC-re majd a Debrecen PC4-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver PC-re majd a Debrecen PC5-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver PC-re majd a Debrecen PC6-ra</t>
+  </si>
+  <si>
+    <t>Budapest Szerver PC-Szeged PC1 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver PC-Szeged PC2 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver PC-Szeged PC3 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver PC-Szeged PC4 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver PC-Szeged PC5 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver PC-Szeged PC6 - Levelezés</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver PC-re majd a Szeged PC6-ra</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver PC-re majd a Szeged PC5-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver PC-re majd a Szeged PC4-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver PC-re majd a Szeged PC3-ra</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver PC-re majd a Szeged PC2-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver PC-re majd a Szeged PC1-re</t>
+  </si>
+  <si>
+    <t>Budapest Szerver1-Debrecen PC1 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver1-Debrecen PC2 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver1-Debrecen PC3 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver1-Debrecen PC4 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver1-Debrecen PC5 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver1-Debrecen PC6 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver1-Szeged PC1 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver1-Szeged PC2 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver1-Szeged PC3 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver1-Szeged PC4 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver1-Szeged PC5 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver1-Szeged PC6 - Levelezés</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver1-re majd a Debrecen PC1-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver1-re majd a Debrecen PC2-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver1-re majd a Debrecen PC3-ra</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver1-re majd a Debrecen PC4-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver1-re majd a Debrecen PC5-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver1-re majd a Szeged PC1-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver1-re majd a Szeged PC2-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver1-re majd a Szeged PC4-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver1-re majd a Szeged PC3-ra</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver1-re majd a Szeged PC5-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver1-re majd a Szeged PC6-ra</t>
+  </si>
+  <si>
+    <t>Összekötő Router-Debrecen PC2 - Levelezés</t>
+  </si>
+  <si>
+    <t>Összekötő Router-Debrecen PC3 - Levelezés</t>
+  </si>
+  <si>
+    <t>Összekötő Router-Debrecen PC4 - Levelezés</t>
+  </si>
+  <si>
+    <t>Összekötő Router-Debrecen PC5 - Levelezés</t>
+  </si>
+  <si>
+    <t>Összekötő Router-Debrecen PC6 - Levelezés</t>
+  </si>
+  <si>
+    <t>Összekötő Router-Debrecen PC1 - Levelezés</t>
+  </si>
+  <si>
+    <t>Összekötő Router-Szeged PC1 - Levelezés</t>
+  </si>
+  <si>
+    <t>Összekötő Router-Szeged PC2 - Levelezés</t>
+  </si>
+  <si>
+    <t>Összekötő Router-Szeged PC3 - Levelezés</t>
+  </si>
+  <si>
+    <t>Összekötő Router-Szeged PC4 - Levelezés</t>
+  </si>
+  <si>
+    <t>Összekötő Router-Szeged PC5 - Levelezés</t>
+  </si>
+  <si>
+    <t>Összekötő Router-Szeged PC6 - Levelezés</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Összekötő Router-re majd a Debrecen PC4-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Összekötő Router-re majd a Debrecen PC1-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Összekötő Router-re majd a Szeged PC1-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Összekötő Router-re majd a Szeged PC2-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Összekötő Router-re majd a Szeged PC3-ra</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Összekötő Router-re majd a Szeged PC4-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Összekötő Router-re majd a Szeged PC5-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Összekötő Router-re majd a Szeged PC6-ra</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver1-re majd a Debrecen PC6-ra</t>
+  </si>
+  <si>
+    <t>Budapest Szerver PC-Budapest PC1 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver PC-Budapest PC2 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver PC-Budapest PC3 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver PC-Budapest PC4 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver PC-Budapest PC5 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver PC-Budapest PC6 - Levelezés</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver PC-re majd a Budapest PC1-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver PC-re majd a Budapest PC2-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver PC-re majd a Budapest PC3-ra</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver PC-re majd a Budapest PC4-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver PC-re majd a Budapest PC5-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver PC-re majd a Budapest PC6-ra</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC1-Székesfehérvár PC3 - Levelezés</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC1-Székesfehérvár PC4 - Levelezés</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC2-Székesfehérvár PC3 - Levelezés</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC2-Székesfehérvár PC4 - Levelezés</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC1-re majd a Székesfehérvár PC3-ra</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC1-re majd a Székesfehérvár PC4-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC2-re majd a Székesfehérvár PC3-ra</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC2-re majd a Székesfehérvár PC4-re</t>
+  </si>
+  <si>
+    <t>Budapest Szerver3-Debrecen Laptop - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver3-Szeged Laptop - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver3-Budapest Laptop1 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver3-Budapest Laptop2 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver3-Összekötő Router - Levelezés</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC1-Összekötő Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC2-Összekötő Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC3-Összekötő Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC4-Összekötő Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Szeged Laptop-Összekötő Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Debrecen Laptop-Összekötő Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Debrecen Laptop-ra majd a Összekötő Router-re</t>
+  </si>
+  <si>
+    <t>Budapest Home Router1-Összekötő Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Home Router2-Összekötő Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Összekötő Router-Debrecen Home Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Összekötő Router-Szeged Home Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver PC-Debrecen Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver PC-Szeged Laptop - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver PC-Szeged Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver Router-Székesfehérvár Router1 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver Router-Székesfehérvár Router2 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver Router-Székesfehérvár Router3 - Levelezés</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC1-re majd a Összekötő Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC2-re majd a Összekötő Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC3-ra majd a Összekötő Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC4-re majd a Összekötő Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Szeged Laptop-ra majd a Összekötő Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Home Router1-re majd a Összekötő Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Home Router2-re majd a Összekötő Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Összekötő Router-re majd a Debrecen Home Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Összekötő Router-re majd a Szeged Home Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver Router-re majd a Székesfehérvár Router1-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver Router-re majd a Székesfehérvár Router2-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver Router-re majd a Székesfehérvár Router3-ra</t>
+  </si>
+  <si>
+    <t>NW-T-102</t>
+  </si>
+  <si>
+    <t>NW-T-103</t>
+  </si>
+  <si>
+    <t>NW-T-104</t>
+  </si>
+  <si>
+    <t>NW-T-105</t>
+  </si>
+  <si>
+    <t>NW-T-106</t>
+  </si>
+  <si>
+    <t>NW-T-107</t>
+  </si>
+  <si>
+    <t>NW-T-108</t>
+  </si>
+  <si>
+    <t>NW-T-109</t>
+  </si>
+  <si>
+    <t>NW-T-110</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Összekötő Router-re majd a Budapest Szerver PC-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver PC-re majd a Debrecen Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver PC-re majd a Szeged Laptop-ra</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver PC-re majd a Szeged Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Összekötő Router-re majd a Debrecen PC2-ra</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Összekötő Router-re majd a Debrecen PC3-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Összekötő Router-re majd a Debrecen PC5-ra</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Összekötő Router-re majd a Debrecen PC6-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver3-ra majd a Debrecen Laptop-ra</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver3-ra majd a Szeged Laptop-ra</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver3-ra majd a Budapest Laptop1-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver3-ra majd a Budapest Laptop2-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver3-ra majd a Összekötő Router-re</t>
+  </si>
+  <si>
+    <t>Csak akkor ha nicsenenek be IP címezve és összekötve az eszközök</t>
+  </si>
+  <si>
+    <t>Hibás lett</t>
+  </si>
+  <si>
+    <t>Budapest Laptop1-Budapest Laptop2 - Levelezés</t>
+  </si>
+  <si>
+    <t>Debrecen Laptop-Szeged Laptop - Levelezés</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Laptop1-re majd a Budapest Laptop2-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Debrecen Laptop-ra majd a Szeged Laptop-ra</t>
+  </si>
+  <si>
+    <t>Budapest Szerver2-Összekötő Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver2-Budapest Szerver Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver2-Budapest Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver2-Székesfehérvár Router1 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver2-Székesfehérvár Router2 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver2-Székesfehérvár Router3 - Levelezés</t>
+  </si>
+  <si>
+    <t>Budapest Szerver2-Debrecen Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver2-re majd a Összekötő Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver2-re majd a Szeged Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver2-re majd a Debrecen Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver2-re majd a Székesfehérvár Router3-ra</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver2-re majd a Székesfehérvár Router2-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver2-re majd a Székesfehérvár Router1-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver2-re majd a Budapest Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Budapest Szerver2-re majd a Budapest Szerver Router-re</t>
+  </si>
+  <si>
+    <t>Budapest Szerver2-Szeged Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC1-Debrecen Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC1-Szeged Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC1-Székesfehérvár Router1 - Levelezés</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC1-Budapest Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC1-Budapest Szerver Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC3-Székesfehérvár Router1 - Levelezés</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC3-Debrecen Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC3-Szeged Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC3-Budapest Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC3-Budapest Szerver Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC3-Debrecen Laptop - Levelezés</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC3-Szeged Laptop - Levelezés</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC4-Székesfehérvár Router1 - Levelezés</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC4-Debrecen Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC4-Szeged Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC4-Budapest Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Székesfehérvár PC4-Budapest Szerver Router - Levelezés</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC1-re majd a Székesfehérvár Router1-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC1-re majd a Debrecen Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC1-re majd a Szeged Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC1-re majd a Budapest Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC1-re majd a Budapest Szerver Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC3-ra majd a Székesfehérvár Router1-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC4-re majd a Székesfehérvár Router1-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC4-re majd a Debrecen Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC4-re majd a Szeged Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC4-re majd a Budapest Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC4-re majd a Budapest Szerver Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC3-ra majd a Szeged Laptop-ra</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC3-ra majd a Debrecen Laptop-ra</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC3-ra majd a Budapest Szerver Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC3-ra majd a budapest Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC3-ra majd a Szeged Router-re</t>
+  </si>
+  <si>
+    <t>Rányomtam a levélre majd rákatintottam a Székesfehérvár PC3-ra majd a Debrecen Router-re</t>
   </si>
 </sst>
 </file>
@@ -633,7 +1197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -677,6 +1241,12 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -899,14 +1469,14 @@
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.6640625" customWidth="1"/>
     <col min="4" max="4" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" customWidth="1"/>
+    <col min="6" max="6" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
+    <col min="8" max="8" width="19.109375" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
     <col min="10" max="10" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -997,7 +1567,7 @@
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1022,7 +1592,7 @@
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -1047,7 +1617,7 @@
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -1072,7 +1642,7 @@
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -1142,7 +1712,7 @@
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
     </row>
-    <row r="9" spans="1:23" ht="142.80000000000001" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" ht="163.19999999999999" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>25</v>
       </c>
@@ -1192,19 +1762,19 @@
         <v>26</v>
       </c>
       <c r="B10" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E10" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="C10" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>140</v>
-      </c>
       <c r="F10" s="15" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G10" s="13">
         <v>45939.538194444445</v>
@@ -1237,19 +1807,19 @@
         <v>27</v>
       </c>
       <c r="B11" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F11" s="15" t="s">
         <v>130</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>141</v>
       </c>
       <c r="G11" s="14">
         <v>45939.541666666664</v>
@@ -1282,19 +1852,19 @@
         <v>28</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>134</v>
+        <v>143</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>285</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G12" s="14">
         <v>45939.543055555558</v>
@@ -1327,19 +1897,19 @@
         <v>29</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>134</v>
+        <v>142</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>285</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G13" s="14">
         <v>45939.547222222223</v>
@@ -1372,19 +1942,19 @@
         <v>30</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>139</v>
+        <v>272</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>143</v>
+        <v>285</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G14" s="14">
         <v>45939.55</v>
@@ -1417,19 +1987,19 @@
         <v>31</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>140</v>
+        <v>285</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>129</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G15" s="14">
         <v>45940.411111111112</v>
@@ -1462,19 +2032,19 @@
         <v>32</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>143</v>
+        <v>285</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G16" s="14">
         <v>45940.413888888892</v>
@@ -1507,19 +2077,19 @@
         <v>33</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>143</v>
+        <v>285</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G17" s="14">
         <v>45940.418055555558</v>
@@ -1552,19 +2122,19 @@
         <v>34</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>143</v>
+        <v>285</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G18" s="14">
         <v>45940.423611111109</v>
@@ -1597,19 +2167,19 @@
         <v>35</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>143</v>
+        <v>285</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G19" s="14">
         <v>45940.431944444441</v>
@@ -1641,17 +2211,33 @@
       <c r="A20" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
+      <c r="B20" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G20" s="14">
+        <v>45940.434027777781</v>
+      </c>
       <c r="H20" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
+      <c r="I20" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
@@ -1670,17 +2256,33 @@
       <c r="A21" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
+      <c r="B21" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G21" s="14">
+        <v>45979.444444444445</v>
+      </c>
       <c r="H21" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
+      <c r="I21" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
@@ -1699,17 +2301,33 @@
       <c r="A22" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
+      <c r="B22" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G22" s="14">
+        <v>45979.445138888892</v>
+      </c>
       <c r="H22" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
+      <c r="I22" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
@@ -1728,17 +2346,33 @@
       <c r="A23" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
+      <c r="B23" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G23" s="14">
+        <v>45979.445833333331</v>
+      </c>
       <c r="H23" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
+      <c r="I23" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J23" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
@@ -1757,17 +2391,33 @@
       <c r="A24" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
+      <c r="B24" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G24" s="14">
+        <v>45979.446527777778</v>
+      </c>
       <c r="H24" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
+      <c r="I24" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J24" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
@@ -1786,17 +2436,33 @@
       <c r="A25" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
+      <c r="B25" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G25" s="14">
+        <v>45979.447222222225</v>
+      </c>
       <c r="H25" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
+      <c r="I25" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
@@ -1815,17 +2481,33 @@
       <c r="A26" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
+      <c r="B26" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G26" s="14">
+        <v>45979.447916666664</v>
+      </c>
       <c r="H26" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
+      <c r="I26" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J26" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
@@ -1840,21 +2522,37 @@
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
     </row>
-    <row r="27" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:23" ht="15.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
+      <c r="B27" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G27" s="14">
+        <v>45979.448611111111</v>
+      </c>
       <c r="H27" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
+      <c r="I27" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J27" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
@@ -1869,21 +2567,37 @@
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
     </row>
-    <row r="28" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:23" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
+      <c r="B28" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G28" s="14">
+        <v>45979.458333333336</v>
+      </c>
       <c r="H28" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
+      <c r="I28" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
@@ -1898,21 +2612,37 @@
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
     </row>
-    <row r="29" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
+      <c r="B29" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G29" s="14">
+        <v>45979.460416666669</v>
+      </c>
       <c r="H29" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
+      <c r="I29" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J29" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
@@ -1927,21 +2657,37 @@
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
     </row>
-    <row r="30" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:23" ht="16.2" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
+      <c r="B30" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G30" s="14">
+        <v>45979.465277777781</v>
+      </c>
       <c r="H30" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
+      <c r="I30" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
@@ -1956,21 +2702,37 @@
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
     </row>
-    <row r="31" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
+      <c r="B31" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G31" s="14">
+        <v>45979.467361111114</v>
+      </c>
       <c r="H31" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
+      <c r="I31" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J31" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
@@ -1985,21 +2747,37 @@
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
     </row>
-    <row r="32" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
+      <c r="B32" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G32" s="14">
+        <v>45979.46875</v>
+      </c>
       <c r="H32" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
+      <c r="I32" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J32" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
@@ -2014,21 +2792,37 @@
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
     </row>
-    <row r="33" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
+      <c r="B33" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G33" s="14">
+        <v>45979.47152777778</v>
+      </c>
       <c r="H33" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
+      <c r="I33" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
@@ -2043,21 +2837,37 @@
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
     </row>
-    <row r="34" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
+      <c r="B34" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G34" s="14">
+        <v>45979.472916666666</v>
+      </c>
       <c r="H34" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
+      <c r="I34" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J34" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
@@ -2072,21 +2882,37 @@
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
     </row>
-    <row r="35" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
+      <c r="B35" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="G35" s="18">
+        <v>45979.474305555559</v>
+      </c>
       <c r="H35" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
+      <c r="I35" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J35" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
@@ -2101,21 +2927,37 @@
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
     </row>
-    <row r="36" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
+      <c r="B36" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G36" s="14">
+        <v>45979.475694444445</v>
+      </c>
       <c r="H36" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
+      <c r="I36" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J36" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
@@ -2130,21 +2972,37 @@
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
     </row>
-    <row r="37" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
+      <c r="B37" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G37" s="14">
+        <v>45979.477083333331</v>
+      </c>
       <c r="H37" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
+      <c r="I37" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J37" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
@@ -2159,21 +3017,37 @@
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
     </row>
-    <row r="38" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
+      <c r="B38" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G38" s="14">
+        <v>45979.479166666664</v>
+      </c>
       <c r="H38" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
+      <c r="I38" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J38" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
@@ -2188,21 +3062,37 @@
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
     </row>
-    <row r="39" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
+      <c r="B39" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G39" s="14">
+        <v>45979.481249999997</v>
+      </c>
       <c r="H39" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
+      <c r="I39" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J39" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
@@ -2217,21 +3107,37 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
     </row>
-    <row r="40" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
+      <c r="B40" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F40" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G40" s="14">
+        <v>45979.482638888891</v>
+      </c>
       <c r="H40" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
+      <c r="I40" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J40" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
@@ -2246,21 +3152,37 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
     </row>
-    <row r="41" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
+      <c r="B41" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F41" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G41" s="14">
+        <v>45979.484722222223</v>
+      </c>
       <c r="H41" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
+      <c r="I41" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J41" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
@@ -2275,21 +3197,37 @@
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
     </row>
-    <row r="42" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
+      <c r="B42" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F42" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G42" s="14">
+        <v>45979.486111111109</v>
+      </c>
       <c r="H42" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10"/>
+      <c r="I42" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J42" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
@@ -2304,21 +3242,37 @@
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
     </row>
-    <row r="43" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
+      <c r="B43" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F43" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G43" s="14">
+        <v>45979.487500000003</v>
+      </c>
       <c r="H43" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
+      <c r="I43" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J43" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
@@ -2333,21 +3287,37 @@
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
     </row>
-    <row r="44" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
+      <c r="B44" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E44" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F44" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G44" s="14">
+        <v>45979.489583333336</v>
+      </c>
       <c r="H44" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
+      <c r="I44" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J44" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
@@ -2362,21 +3332,37 @@
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
     </row>
-    <row r="45" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
+      <c r="B45" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E45" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G45" s="14">
+        <v>45979.491666666669</v>
+      </c>
       <c r="H45" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
+      <c r="I45" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J45" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
@@ -2391,21 +3377,37 @@
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
     </row>
-    <row r="46" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
+      <c r="B46" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E46" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F46" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G46" s="14">
+        <v>45979.493055555555</v>
+      </c>
       <c r="H46" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
+      <c r="I46" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J46" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
@@ -2420,21 +3422,37 @@
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
     </row>
-    <row r="47" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
+      <c r="B47" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E47" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F47" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G47" s="14">
+        <v>45979.495138888888</v>
+      </c>
       <c r="H47" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
+      <c r="I47" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J47" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
@@ -2449,21 +3467,37 @@
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
     </row>
-    <row r="48" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
+      <c r="B48" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E48" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F48" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G48" s="14">
+        <v>45979.496527777781</v>
+      </c>
       <c r="H48" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
+      <c r="I48" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J48" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
@@ -2478,21 +3512,37 @@
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
     </row>
-    <row r="49" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
+      <c r="B49" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E49" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G49" s="14">
+        <v>45979.497916666667</v>
+      </c>
       <c r="H49" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
+      <c r="I49" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J49" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
@@ -2507,21 +3557,37 @@
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
     </row>
-    <row r="50" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B50" s="10"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
+      <c r="B50" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F50" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G50" s="14">
+        <v>45979.5</v>
+      </c>
       <c r="H50" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
+      <c r="I50" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J50" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
@@ -2536,21 +3602,37 @@
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
     </row>
-    <row r="51" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
+      <c r="B51" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E51" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F51" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G51" s="14">
+        <v>45979.501388888886</v>
+      </c>
       <c r="H51" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
+      <c r="I51" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J51" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
@@ -2565,21 +3647,37 @@
       <c r="V51" s="3"/>
       <c r="W51" s="3"/>
     </row>
-    <row r="52" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B52" s="10"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="10"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="10"/>
+      <c r="B52" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E52" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F52" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G52" s="14">
+        <v>45979.503472222219</v>
+      </c>
       <c r="H52" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I52" s="10"/>
-      <c r="J52" s="10"/>
+      <c r="I52" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J52" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
@@ -2594,21 +3692,37 @@
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
     </row>
-    <row r="53" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
+      <c r="B53" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E53" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F53" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G53" s="14">
+        <v>45979.505555555559</v>
+      </c>
       <c r="H53" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
+      <c r="I53" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J53" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
@@ -2623,21 +3737,37 @@
       <c r="V53" s="3"/>
       <c r="W53" s="3"/>
     </row>
-    <row r="54" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:23" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
+      <c r="B54" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F54" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G54" s="14">
+        <v>46002.423611111109</v>
+      </c>
       <c r="H54" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
+      <c r="I54" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J54" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
@@ -2652,21 +3782,37 @@
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
     </row>
-    <row r="55" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B55" s="10"/>
-      <c r="C55" s="10"/>
-      <c r="D55" s="10"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="10"/>
-      <c r="G55" s="10"/>
+      <c r="B55" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F55" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G55" s="14">
+        <v>46002.425000000003</v>
+      </c>
       <c r="H55" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I55" s="10"/>
-      <c r="J55" s="10"/>
+      <c r="I55" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J55" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -2681,21 +3827,37 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
     </row>
-    <row r="56" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B56" s="10"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="10"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="10"/>
-      <c r="G56" s="10"/>
+      <c r="B56" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F56" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G56" s="14">
+        <v>46002.427083333336</v>
+      </c>
       <c r="H56" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
+      <c r="I56" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J56" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
@@ -2710,21 +3872,37 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
     </row>
-    <row r="57" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B57" s="10"/>
-      <c r="C57" s="10"/>
-      <c r="D57" s="10"/>
-      <c r="E57" s="10"/>
-      <c r="F57" s="10"/>
-      <c r="G57" s="10"/>
+      <c r="B57" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F57" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G57" s="14">
+        <v>46002.430555555555</v>
+      </c>
       <c r="H57" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I57" s="10"/>
-      <c r="J57" s="10"/>
+      <c r="I57" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J57" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K57" s="3"/>
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
@@ -2739,21 +3917,37 @@
       <c r="V57" s="3"/>
       <c r="W57" s="3"/>
     </row>
-    <row r="58" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B58" s="10"/>
-      <c r="C58" s="10"/>
-      <c r="D58" s="10"/>
-      <c r="E58" s="10"/>
-      <c r="F58" s="10"/>
-      <c r="G58" s="10"/>
+      <c r="B58" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F58" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G58" s="14">
+        <v>46002.431944444441</v>
+      </c>
       <c r="H58" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I58" s="10"/>
-      <c r="J58" s="10"/>
+      <c r="I58" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J58" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K58" s="3"/>
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
@@ -2768,21 +3962,37 @@
       <c r="V58" s="3"/>
       <c r="W58" s="3"/>
     </row>
-    <row r="59" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B59" s="10"/>
-      <c r="C59" s="10"/>
-      <c r="D59" s="10"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="10"/>
-      <c r="G59" s="10"/>
+      <c r="B59" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F59" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G59" s="14">
+        <v>46002.433333333334</v>
+      </c>
       <c r="H59" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I59" s="10"/>
-      <c r="J59" s="10"/>
+      <c r="I59" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J59" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K59" s="3"/>
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
@@ -2797,21 +4007,37 @@
       <c r="V59" s="3"/>
       <c r="W59" s="3"/>
     </row>
-    <row r="60" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B60" s="10"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="10"/>
-      <c r="E60" s="10"/>
-      <c r="F60" s="10"/>
-      <c r="G60" s="10"/>
+      <c r="B60" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="D60" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F60" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G60" s="14">
+        <v>46009.436111111114</v>
+      </c>
       <c r="H60" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I60" s="10"/>
-      <c r="J60" s="10"/>
+      <c r="I60" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J60" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K60" s="3"/>
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
@@ -2826,21 +4052,37 @@
       <c r="V60" s="3"/>
       <c r="W60" s="3"/>
     </row>
-    <row r="61" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="B61" s="10"/>
-      <c r="C61" s="10"/>
-      <c r="D61" s="10"/>
-      <c r="E61" s="10"/>
-      <c r="F61" s="10"/>
-      <c r="G61" s="10"/>
+      <c r="B61" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="D61" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F61" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G61" s="14">
+        <v>46009.4375</v>
+      </c>
       <c r="H61" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
+      <c r="I61" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J61" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K61" s="3"/>
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
@@ -2855,21 +4097,37 @@
       <c r="V61" s="3"/>
       <c r="W61" s="3"/>
     </row>
-    <row r="62" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="B62" s="10"/>
-      <c r="C62" s="10"/>
-      <c r="D62" s="10"/>
-      <c r="E62" s="10"/>
-      <c r="F62" s="10"/>
-      <c r="G62" s="10"/>
+      <c r="B62" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="D62" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F62" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G62" s="14">
+        <v>46009.439583333333</v>
+      </c>
       <c r="H62" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I62" s="10"/>
-      <c r="J62" s="10"/>
+      <c r="I62" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J62" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K62" s="3"/>
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
@@ -2884,21 +4142,37 @@
       <c r="V62" s="3"/>
       <c r="W62" s="3"/>
     </row>
-    <row r="63" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B63" s="10"/>
-      <c r="C63" s="10"/>
-      <c r="D63" s="10"/>
-      <c r="E63" s="10"/>
-      <c r="F63" s="10"/>
-      <c r="G63" s="10"/>
+      <c r="B63" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F63" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G63" s="14">
+        <v>46009.440972222219</v>
+      </c>
       <c r="H63" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I63" s="10"/>
-      <c r="J63" s="10"/>
+      <c r="I63" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J63" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K63" s="3"/>
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
@@ -2913,21 +4187,37 @@
       <c r="V63" s="3"/>
       <c r="W63" s="3"/>
     </row>
-    <row r="64" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="B64" s="10"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="10"/>
-      <c r="E64" s="10"/>
-      <c r="F64" s="10"/>
-      <c r="G64" s="10"/>
+      <c r="B64" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="C64" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="D64" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F64" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G64" s="14">
+        <v>46009.442361111112</v>
+      </c>
       <c r="H64" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I64" s="10"/>
-      <c r="J64" s="10"/>
+      <c r="I64" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J64" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K64" s="3"/>
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
@@ -2942,21 +4232,37 @@
       <c r="V64" s="3"/>
       <c r="W64" s="3"/>
     </row>
-    <row r="65" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B65" s="10"/>
-      <c r="C65" s="10"/>
-      <c r="D65" s="10"/>
-      <c r="E65" s="10"/>
-      <c r="F65" s="10"/>
-      <c r="G65" s="10"/>
+      <c r="B65" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="D65" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F65" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G65" s="14">
+        <v>46009.444444444445</v>
+      </c>
       <c r="H65" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I65" s="10"/>
-      <c r="J65" s="10"/>
+      <c r="I65" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J65" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K65" s="3"/>
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
@@ -2971,21 +4277,37 @@
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
     </row>
-    <row r="66" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B66" s="10"/>
-      <c r="C66" s="10"/>
-      <c r="D66" s="10"/>
-      <c r="E66" s="10"/>
-      <c r="F66" s="10"/>
-      <c r="G66" s="10"/>
+      <c r="B66" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F66" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G66" s="14">
+        <v>46009.445833333331</v>
+      </c>
       <c r="H66" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I66" s="10"/>
-      <c r="J66" s="10"/>
+      <c r="I66" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J66" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K66" s="3"/>
       <c r="L66" s="3"/>
       <c r="M66" s="3"/>
@@ -3000,21 +4322,37 @@
       <c r="V66" s="3"/>
       <c r="W66" s="3"/>
     </row>
-    <row r="67" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B67" s="10"/>
-      <c r="C67" s="10"/>
-      <c r="D67" s="10"/>
-      <c r="E67" s="10"/>
-      <c r="F67" s="10"/>
-      <c r="G67" s="10"/>
+      <c r="B67" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="D67" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F67" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G67" s="14">
+        <v>46009.447222222225</v>
+      </c>
       <c r="H67" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I67" s="10"/>
-      <c r="J67" s="10"/>
+      <c r="I67" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J67" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
@@ -3029,21 +4367,37 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
     </row>
-    <row r="68" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="B68" s="10"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="10"/>
-      <c r="E68" s="10"/>
-      <c r="F68" s="10"/>
-      <c r="G68" s="10"/>
+      <c r="B68" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E68" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F68" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G68" s="14">
+        <v>46009.449305555558</v>
+      </c>
       <c r="H68" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I68" s="10"/>
-      <c r="J68" s="10"/>
+      <c r="I68" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J68" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K68" s="3"/>
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
@@ -3058,21 +4412,37 @@
       <c r="V68" s="3"/>
       <c r="W68" s="3"/>
     </row>
-    <row r="69" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:23" ht="16.8" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="B69" s="10"/>
-      <c r="C69" s="10"/>
-      <c r="D69" s="10"/>
-      <c r="E69" s="10"/>
-      <c r="F69" s="10"/>
-      <c r="G69" s="10"/>
+      <c r="B69" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E69" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F69" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="G69" s="14">
+        <v>46009.454861111109</v>
+      </c>
       <c r="H69" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I69" s="10"/>
-      <c r="J69" s="10"/>
+      <c r="I69" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="J69" s="15" t="s">
+        <v>25</v>
+      </c>
       <c r="K69" s="3"/>
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
@@ -3087,21 +4457,37 @@
       <c r="V69" s="3"/>
       <c r="W69" s="3"/>
     </row>
-    <row r="70" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="B70" s="10"/>
-      <c r="C70" s="10"/>
-      <c r="D70" s="10"/>
-      <c r="E70" s="10"/>
-      <c r="F70" s="10"/>
-      <c r="G70" s="10"/>
+      <c r="B70" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="D70" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E70" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F70" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="G70" s="14">
+        <v>46009.456250000003</v>
+      </c>
       <c r="H70" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I70" s="10"/>
-      <c r="J70" s="10"/>
+      <c r="I70" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="J70" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="K70" s="3"/>
       <c r="L70" s="3"/>
       <c r="M70" s="3"/>
@@ -3116,21 +4502,37 @@
       <c r="V70" s="3"/>
       <c r="W70" s="3"/>
     </row>
-    <row r="71" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B71" s="10"/>
-      <c r="C71" s="10"/>
-      <c r="D71" s="10"/>
-      <c r="E71" s="10"/>
-      <c r="F71" s="10"/>
-      <c r="G71" s="10"/>
+      <c r="B71" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="C71" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="D71" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E71" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F71" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="G71" s="14">
+        <v>46009.458333333336</v>
+      </c>
       <c r="H71" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I71" s="10"/>
-      <c r="J71" s="10"/>
+      <c r="I71" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="J71" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="K71" s="3"/>
       <c r="L71" s="3"/>
       <c r="M71" s="3"/>
@@ -3145,21 +4547,37 @@
       <c r="V71" s="3"/>
       <c r="W71" s="3"/>
     </row>
-    <row r="72" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B72" s="10"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="10"/>
-      <c r="E72" s="10"/>
-      <c r="F72" s="10"/>
-      <c r="G72" s="10"/>
+      <c r="B72" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D72" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E72" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F72" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="G72" s="14">
+        <v>46009.459722222222</v>
+      </c>
       <c r="H72" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I72" s="10"/>
-      <c r="J72" s="10"/>
+      <c r="I72" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="J72" s="15" t="s">
+        <v>28</v>
+      </c>
       <c r="K72" s="3"/>
       <c r="L72" s="3"/>
       <c r="M72" s="3"/>
@@ -3174,21 +4592,37 @@
       <c r="V72" s="3"/>
       <c r="W72" s="3"/>
     </row>
-    <row r="73" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:23" ht="16.8" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="B73" s="10"/>
-      <c r="C73" s="10"/>
-      <c r="D73" s="10"/>
-      <c r="E73" s="10"/>
-      <c r="F73" s="10"/>
-      <c r="G73" s="10"/>
+      <c r="B73" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="D73" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E73" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F73" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="G73" s="14">
+        <v>46009.461111111108</v>
+      </c>
       <c r="H73" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I73" s="10"/>
-      <c r="J73" s="10"/>
+      <c r="I73" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="J73" s="15" t="s">
+        <v>29</v>
+      </c>
       <c r="K73" s="3"/>
       <c r="L73" s="3"/>
       <c r="M73" s="3"/>
@@ -3203,21 +4637,37 @@
       <c r="V73" s="3"/>
       <c r="W73" s="3"/>
     </row>
-    <row r="74" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:23" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="B74" s="10"/>
-      <c r="C74" s="10"/>
-      <c r="D74" s="10"/>
-      <c r="E74" s="10"/>
-      <c r="F74" s="10"/>
-      <c r="G74" s="10"/>
+      <c r="B74" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="D74" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E74" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F74" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="G74" s="14">
+        <v>46009.463194444441</v>
+      </c>
       <c r="H74" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I74" s="10"/>
-      <c r="J74" s="10"/>
+      <c r="I74" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="J74" s="15" t="s">
+        <v>30</v>
+      </c>
       <c r="K74" s="3"/>
       <c r="L74" s="3"/>
       <c r="M74" s="3"/>
@@ -3232,21 +4682,37 @@
       <c r="V74" s="3"/>
       <c r="W74" s="3"/>
     </row>
-    <row r="75" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B75" s="10"/>
-      <c r="C75" s="10"/>
-      <c r="D75" s="10"/>
-      <c r="E75" s="10"/>
-      <c r="F75" s="10"/>
-      <c r="G75" s="10"/>
+      <c r="B75" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="D75" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E75" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F75" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="G75" s="14">
+        <v>46009.465277777781</v>
+      </c>
       <c r="H75" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I75" s="10"/>
-      <c r="J75" s="10"/>
+      <c r="I75" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="J75" s="15" t="s">
+        <v>31</v>
+      </c>
       <c r="K75" s="3"/>
       <c r="L75" s="3"/>
       <c r="M75" s="3"/>
@@ -3261,21 +4727,37 @@
       <c r="V75" s="3"/>
       <c r="W75" s="3"/>
     </row>
-    <row r="76" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B76" s="10"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="10"/>
-      <c r="E76" s="10"/>
-      <c r="F76" s="10"/>
-      <c r="G76" s="10"/>
+      <c r="B76" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="D76" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E76" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F76" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="G76" s="14">
+        <v>46009.467361111114</v>
+      </c>
       <c r="H76" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I76" s="10"/>
-      <c r="J76" s="10"/>
+      <c r="I76" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="J76" s="15" t="s">
+        <v>32</v>
+      </c>
       <c r="K76" s="3"/>
       <c r="L76" s="3"/>
       <c r="M76" s="3"/>
@@ -3290,21 +4772,37 @@
       <c r="V76" s="3"/>
       <c r="W76" s="3"/>
     </row>
-    <row r="77" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:23" ht="16.8" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="B77" s="10"/>
-      <c r="C77" s="10"/>
-      <c r="D77" s="10"/>
-      <c r="E77" s="10"/>
-      <c r="F77" s="10"/>
-      <c r="G77" s="10"/>
+      <c r="B77" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="D77" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E77" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F77" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="G77" s="14">
+        <v>46009.46875</v>
+      </c>
       <c r="H77" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I77" s="10"/>
-      <c r="J77" s="10"/>
+      <c r="I77" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="J77" s="15" t="s">
+        <v>33</v>
+      </c>
       <c r="K77" s="3"/>
       <c r="L77" s="3"/>
       <c r="M77" s="3"/>
@@ -3319,21 +4817,37 @@
       <c r="V77" s="3"/>
       <c r="W77" s="3"/>
     </row>
-    <row r="78" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="B78" s="10"/>
-      <c r="C78" s="10"/>
-      <c r="D78" s="10"/>
-      <c r="E78" s="10"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="10"/>
+      <c r="B78" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="D78" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E78" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F78" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="G78" s="14">
+        <v>46009.47152777778</v>
+      </c>
       <c r="H78" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I78" s="10"/>
-      <c r="J78" s="10"/>
+      <c r="I78" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="J78" s="15" t="s">
+        <v>34</v>
+      </c>
       <c r="K78" s="3"/>
       <c r="L78" s="3"/>
       <c r="M78" s="3"/>
@@ -3348,21 +4862,37 @@
       <c r="V78" s="3"/>
       <c r="W78" s="3"/>
     </row>
-    <row r="79" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:23" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="B79" s="10"/>
-      <c r="C79" s="10"/>
-      <c r="D79" s="10"/>
-      <c r="E79" s="10"/>
-      <c r="F79" s="10"/>
-      <c r="G79" s="10"/>
+      <c r="B79" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="C79" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="D79" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E79" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F79" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G79" s="14">
+        <v>46009.479166666664</v>
+      </c>
       <c r="H79" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I79" s="10"/>
-      <c r="J79" s="10"/>
+      <c r="I79" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J79" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K79" s="3"/>
       <c r="L79" s="3"/>
       <c r="M79" s="3"/>
@@ -3377,21 +4907,37 @@
       <c r="V79" s="3"/>
       <c r="W79" s="3"/>
     </row>
-    <row r="80" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:23" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="B80" s="10"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="10"/>
-      <c r="E80" s="10"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="10"/>
+      <c r="B80" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="C80" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="D80" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E80" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F80" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G80" s="14">
+        <v>46009.480555555558</v>
+      </c>
       <c r="H80" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I80" s="10"/>
-      <c r="J80" s="10"/>
+      <c r="I80" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J80" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K80" s="3"/>
       <c r="L80" s="3"/>
       <c r="M80" s="3"/>
@@ -3406,21 +4952,37 @@
       <c r="V80" s="3"/>
       <c r="W80" s="3"/>
     </row>
-    <row r="81" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:23" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="B81" s="10"/>
-      <c r="C81" s="10"/>
-      <c r="D81" s="10"/>
-      <c r="E81" s="10"/>
-      <c r="F81" s="10"/>
-      <c r="G81" s="10"/>
+      <c r="B81" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="C81" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="D81" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E81" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F81" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G81" s="14">
+        <v>46009.481944444444</v>
+      </c>
       <c r="H81" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I81" s="10"/>
-      <c r="J81" s="10"/>
+      <c r="I81" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J81" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K81" s="3"/>
       <c r="L81" s="3"/>
       <c r="M81" s="3"/>
@@ -3435,21 +4997,37 @@
       <c r="V81" s="3"/>
       <c r="W81" s="3"/>
     </row>
-    <row r="82" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:23" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="B82" s="10"/>
-      <c r="C82" s="10"/>
-      <c r="D82" s="10"/>
-      <c r="E82" s="10"/>
-      <c r="F82" s="10"/>
-      <c r="G82" s="10"/>
+      <c r="B82" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="C82" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D82" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E82" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F82" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G82" s="14">
+        <v>46009.484027777777</v>
+      </c>
       <c r="H82" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I82" s="10"/>
-      <c r="J82" s="10"/>
+      <c r="I82" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J82" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
@@ -3464,21 +5042,37 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
     </row>
-    <row r="83" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:23" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="B83" s="10"/>
-      <c r="C83" s="10"/>
-      <c r="D83" s="10"/>
-      <c r="E83" s="10"/>
-      <c r="F83" s="10"/>
-      <c r="G83" s="10"/>
+      <c r="B83" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="C83" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="D83" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E83" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F83" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G83" s="14">
+        <v>46009.486111111109</v>
+      </c>
       <c r="H83" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I83" s="10"/>
-      <c r="J83" s="10"/>
+      <c r="I83" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J83" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K83" s="3"/>
       <c r="L83" s="3"/>
       <c r="M83" s="3"/>
@@ -3493,21 +5087,37 @@
       <c r="V83" s="3"/>
       <c r="W83" s="3"/>
     </row>
-    <row r="84" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:23" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="B84" s="10"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="10"/>
-      <c r="E84" s="10"/>
-      <c r="F84" s="10"/>
-      <c r="G84" s="10"/>
+      <c r="B84" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="D84" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E84" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F84" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G84" s="14">
+        <v>46009.488194444442</v>
+      </c>
       <c r="H84" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I84" s="10"/>
-      <c r="J84" s="10"/>
+      <c r="I84" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J84" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K84" s="3"/>
       <c r="L84" s="3"/>
       <c r="M84" s="3"/>
@@ -3522,21 +5132,37 @@
       <c r="V84" s="3"/>
       <c r="W84" s="3"/>
     </row>
-    <row r="85" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:23" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B85" s="10"/>
-      <c r="C85" s="10"/>
-      <c r="D85" s="10"/>
-      <c r="E85" s="10"/>
-      <c r="F85" s="10"/>
-      <c r="G85" s="10"/>
+      <c r="B85" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="C85" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="D85" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E85" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F85" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G85" s="14">
+        <v>46009.489583333336</v>
+      </c>
       <c r="H85" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I85" s="10"/>
-      <c r="J85" s="10"/>
+      <c r="I85" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J85" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K85" s="3"/>
       <c r="L85" s="3"/>
       <c r="M85" s="3"/>
@@ -3551,21 +5177,37 @@
       <c r="V85" s="3"/>
       <c r="W85" s="3"/>
     </row>
-    <row r="86" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:23" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="B86" s="10"/>
-      <c r="C86" s="10"/>
-      <c r="D86" s="10"/>
-      <c r="E86" s="10"/>
-      <c r="F86" s="10"/>
-      <c r="G86" s="10"/>
+      <c r="B86" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="C86" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="D86" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E86" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F86" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G86" s="14">
+        <v>46009.490972222222</v>
+      </c>
       <c r="H86" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I86" s="10"/>
-      <c r="J86" s="10"/>
+      <c r="I86" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J86" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K86" s="3"/>
       <c r="L86" s="3"/>
       <c r="M86" s="3"/>
@@ -3580,21 +5222,37 @@
       <c r="V86" s="3"/>
       <c r="W86" s="3"/>
     </row>
-    <row r="87" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:23" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="B87" s="10"/>
-      <c r="C87" s="10"/>
-      <c r="D87" s="10"/>
-      <c r="E87" s="10"/>
-      <c r="F87" s="10"/>
-      <c r="G87" s="10"/>
+      <c r="B87" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="C87" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="D87" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E87" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F87" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G87" s="14">
+        <v>46009.493055555555</v>
+      </c>
       <c r="H87" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I87" s="10"/>
-      <c r="J87" s="10"/>
+      <c r="I87" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J87" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K87" s="3"/>
       <c r="L87" s="3"/>
       <c r="M87" s="3"/>
@@ -3609,21 +5267,37 @@
       <c r="V87" s="3"/>
       <c r="W87" s="3"/>
     </row>
-    <row r="88" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:23" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B88" s="10"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="10"/>
-      <c r="E88" s="10"/>
-      <c r="F88" s="10"/>
-      <c r="G88" s="10"/>
+      <c r="B88" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="C88" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="D88" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E88" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F88" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G88" s="14">
+        <v>46009.493750000001</v>
+      </c>
       <c r="H88" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I88" s="10"/>
-      <c r="J88" s="10"/>
+      <c r="I88" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J88" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K88" s="3"/>
       <c r="L88" s="3"/>
       <c r="M88" s="3"/>
@@ -3638,21 +5312,37 @@
       <c r="V88" s="3"/>
       <c r="W88" s="3"/>
     </row>
-    <row r="89" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B89" s="3"/>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3"/>
-      <c r="E89" s="3"/>
-      <c r="F89" s="3"/>
-      <c r="G89" s="3"/>
+      <c r="B89" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="C89" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="D89" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E89" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F89" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G89" s="14">
+        <v>46009.495833333334</v>
+      </c>
       <c r="H89" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I89" s="3"/>
-      <c r="J89" s="3"/>
+      <c r="I89" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J89" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K89" s="3"/>
       <c r="L89" s="3"/>
       <c r="M89" s="3"/>
@@ -3667,21 +5357,37 @@
       <c r="V89" s="3"/>
       <c r="W89" s="3"/>
     </row>
-    <row r="90" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B90" s="3"/>
-      <c r="C90" s="3"/>
-      <c r="D90" s="3"/>
-      <c r="E90" s="3"/>
-      <c r="F90" s="3"/>
-      <c r="G90" s="3"/>
+      <c r="B90" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="C90" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="D90" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E90" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F90" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G90" s="14">
+        <v>46009.497916666667</v>
+      </c>
       <c r="H90" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I90" s="3"/>
-      <c r="J90" s="3"/>
+      <c r="I90" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J90" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
@@ -3696,21 +5402,37 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
     </row>
-    <row r="91" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="B91" s="3"/>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3"/>
-      <c r="E91" s="3"/>
-      <c r="F91" s="3"/>
-      <c r="G91" s="3"/>
+      <c r="B91" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="C91" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="D91" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E91" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F91" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G91" s="14">
+        <v>46009.5</v>
+      </c>
       <c r="H91" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I91" s="3"/>
-      <c r="J91" s="3"/>
+      <c r="I91" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J91" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K91" s="3"/>
       <c r="L91" s="3"/>
       <c r="M91" s="3"/>
@@ -3725,21 +5447,37 @@
       <c r="V91" s="3"/>
       <c r="W91" s="3"/>
     </row>
-    <row r="92" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="B92" s="3"/>
-      <c r="C92" s="3"/>
-      <c r="D92" s="3"/>
-      <c r="E92" s="3"/>
-      <c r="F92" s="3"/>
-      <c r="G92" s="3"/>
+      <c r="B92" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="C92" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="D92" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E92" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F92" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G92" s="14">
+        <v>46009.502083333333</v>
+      </c>
       <c r="H92" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I92" s="3"/>
-      <c r="J92" s="3"/>
+      <c r="I92" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J92" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K92" s="3"/>
       <c r="L92" s="3"/>
       <c r="M92" s="3"/>
@@ -3754,21 +5492,37 @@
       <c r="V92" s="3"/>
       <c r="W92" s="3"/>
     </row>
-    <row r="93" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B93" s="3"/>
-      <c r="C93" s="3"/>
-      <c r="D93" s="3"/>
-      <c r="E93" s="3"/>
-      <c r="F93" s="3"/>
-      <c r="G93" s="3"/>
+      <c r="B93" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="C93" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D93" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E93" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F93" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G93" s="14">
+        <v>46009.503472222219</v>
+      </c>
       <c r="H93" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I93" s="3"/>
-      <c r="J93" s="3"/>
+      <c r="I93" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J93" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K93" s="3"/>
       <c r="L93" s="3"/>
       <c r="M93" s="3"/>
@@ -3783,21 +5537,37 @@
       <c r="V93" s="3"/>
       <c r="W93" s="3"/>
     </row>
-    <row r="94" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="B94" s="3"/>
-      <c r="C94" s="3"/>
-      <c r="D94" s="3"/>
-      <c r="E94" s="3"/>
-      <c r="F94" s="3"/>
-      <c r="G94" s="3"/>
+      <c r="B94" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="C94" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="D94" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E94" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F94" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G94" s="14">
+        <v>46009.505555555559</v>
+      </c>
       <c r="H94" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I94" s="3"/>
-      <c r="J94" s="3"/>
+      <c r="I94" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J94" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K94" s="3"/>
       <c r="L94" s="3"/>
       <c r="M94" s="3"/>
@@ -3812,21 +5582,37 @@
       <c r="V94" s="3"/>
       <c r="W94" s="3"/>
     </row>
-    <row r="95" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B95" s="3"/>
-      <c r="C95" s="3"/>
-      <c r="D95" s="3"/>
-      <c r="E95" s="3"/>
-      <c r="F95" s="3"/>
-      <c r="G95" s="3"/>
+      <c r="B95" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="C95" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="D95" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E95" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F95" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G95" s="14">
+        <v>46009.507638888892</v>
+      </c>
       <c r="H95" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I95" s="3"/>
-      <c r="J95" s="3"/>
+      <c r="I95" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J95" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
@@ -3841,21 +5627,37 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
     </row>
-    <row r="96" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B96" s="3"/>
-      <c r="C96" s="3"/>
-      <c r="D96" s="3"/>
-      <c r="E96" s="3"/>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3"/>
+      <c r="B96" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="C96" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="D96" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E96" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F96" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G96" s="14">
+        <v>46009.510416666664</v>
+      </c>
       <c r="H96" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I96" s="3"/>
-      <c r="J96" s="3"/>
+      <c r="I96" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J96" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K96" s="3"/>
       <c r="L96" s="3"/>
       <c r="M96" s="3"/>
@@ -3870,21 +5672,37 @@
       <c r="V96" s="3"/>
       <c r="W96" s="3"/>
     </row>
-    <row r="97" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="B97" s="3"/>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3"/>
+      <c r="B97" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="C97" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="D97" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E97" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F97" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G97" s="14">
+        <v>46009.511805555558</v>
+      </c>
       <c r="H97" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I97" s="3"/>
-      <c r="J97" s="3"/>
+      <c r="I97" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J97" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K97" s="3"/>
       <c r="L97" s="3"/>
       <c r="M97" s="3"/>
@@ -3899,21 +5717,37 @@
       <c r="V97" s="3"/>
       <c r="W97" s="3"/>
     </row>
-    <row r="98" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B98" s="3"/>
-      <c r="C98" s="3"/>
-      <c r="D98" s="3"/>
-      <c r="E98" s="3"/>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3"/>
+      <c r="B98" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="C98" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="D98" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E98" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F98" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G98" s="14">
+        <v>46009.510416666664</v>
+      </c>
       <c r="H98" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I98" s="3"/>
-      <c r="J98" s="3"/>
+      <c r="I98" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J98" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K98" s="3"/>
       <c r="L98" s="3"/>
       <c r="M98" s="3"/>
@@ -3928,21 +5762,37 @@
       <c r="V98" s="3"/>
       <c r="W98" s="3"/>
     </row>
-    <row r="99" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B99" s="3"/>
-      <c r="C99" s="3"/>
-      <c r="D99" s="3"/>
-      <c r="E99" s="3"/>
-      <c r="F99" s="3"/>
-      <c r="G99" s="3"/>
+      <c r="B99" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="C99" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="D99" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E99" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F99" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G99" s="14">
+        <v>46009.541666666664</v>
+      </c>
       <c r="H99" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I99" s="3"/>
-      <c r="J99" s="3"/>
+      <c r="I99" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J99" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K99" s="3"/>
       <c r="L99" s="3"/>
       <c r="M99" s="3"/>
@@ -3957,21 +5807,37 @@
       <c r="V99" s="3"/>
       <c r="W99" s="3"/>
     </row>
-    <row r="100" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B100" s="3"/>
-      <c r="C100" s="3"/>
-      <c r="D100" s="3"/>
-      <c r="E100" s="3"/>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3"/>
+      <c r="B100" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="C100" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="D100" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E100" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F100" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G100" s="14">
+        <v>46009.543055555558</v>
+      </c>
       <c r="H100" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I100" s="3"/>
-      <c r="J100" s="3"/>
+      <c r="I100" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J100" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K100" s="3"/>
       <c r="L100" s="3"/>
       <c r="M100" s="3"/>
@@ -3986,21 +5852,37 @@
       <c r="V100" s="3"/>
       <c r="W100" s="3"/>
     </row>
-    <row r="101" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B101" s="3"/>
-      <c r="C101" s="3"/>
-      <c r="D101" s="3"/>
-      <c r="E101" s="3"/>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3"/>
+      <c r="B101" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="C101" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="D101" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E101" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F101" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G101" s="14">
+        <v>46009.544444444444</v>
+      </c>
       <c r="H101" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I101" s="3"/>
-      <c r="J101" s="3"/>
+      <c r="I101" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J101" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K101" s="3"/>
       <c r="L101" s="3"/>
       <c r="M101" s="3"/>
@@ -4015,21 +5897,37 @@
       <c r="V101" s="3"/>
       <c r="W101" s="3"/>
     </row>
-    <row r="102" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B102" s="3"/>
-      <c r="C102" s="3"/>
-      <c r="D102" s="3"/>
-      <c r="E102" s="3"/>
-      <c r="F102" s="3"/>
-      <c r="G102" s="3"/>
+      <c r="B102" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="C102" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="D102" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E102" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F102" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G102" s="14">
+        <v>46009.546527777777</v>
+      </c>
       <c r="H102" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I102" s="3"/>
-      <c r="J102" s="3"/>
+      <c r="I102" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J102" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K102" s="3"/>
       <c r="L102" s="3"/>
       <c r="M102" s="3"/>
@@ -4044,21 +5942,37 @@
       <c r="V102" s="3"/>
       <c r="W102" s="3"/>
     </row>
-    <row r="103" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="B103" s="3"/>
-      <c r="C103" s="3"/>
-      <c r="D103" s="3"/>
-      <c r="E103" s="3"/>
-      <c r="F103" s="3"/>
-      <c r="G103" s="3"/>
+      <c r="B103" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="C103" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="D103" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E103" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F103" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G103" s="14">
+        <v>46009.54791666667</v>
+      </c>
       <c r="H103" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I103" s="3"/>
-      <c r="J103" s="3"/>
+      <c r="I103" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J103" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K103" s="3"/>
       <c r="L103" s="3"/>
       <c r="M103" s="3"/>
@@ -4073,21 +5987,37 @@
       <c r="V103" s="3"/>
       <c r="W103" s="3"/>
     </row>
-    <row r="104" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B104" s="3"/>
-      <c r="C104" s="3"/>
-      <c r="D104" s="3"/>
-      <c r="E104" s="3"/>
-      <c r="F104" s="3"/>
-      <c r="G104" s="3"/>
+      <c r="B104" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="C104" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="D104" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E104" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F104" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G104" s="14">
+        <v>46009.55</v>
+      </c>
       <c r="H104" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I104" s="3"/>
-      <c r="J104" s="3"/>
+      <c r="I104" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J104" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K104" s="3"/>
       <c r="L104" s="3"/>
       <c r="M104" s="3"/>
@@ -4102,21 +6032,37 @@
       <c r="V104" s="3"/>
       <c r="W104" s="3"/>
     </row>
-    <row r="105" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="B105" s="3"/>
-      <c r="C105" s="3"/>
-      <c r="D105" s="3"/>
-      <c r="E105" s="3"/>
-      <c r="F105" s="3"/>
-      <c r="G105" s="3"/>
+      <c r="B105" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="C105" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="D105" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E105" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F105" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G105" s="14">
+        <v>46009.552777777775</v>
+      </c>
       <c r="H105" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I105" s="3"/>
-      <c r="J105" s="3"/>
+      <c r="I105" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J105" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K105" s="3"/>
       <c r="L105" s="3"/>
       <c r="M105" s="3"/>
@@ -4131,21 +6077,37 @@
       <c r="V105" s="3"/>
       <c r="W105" s="3"/>
     </row>
-    <row r="106" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="B106" s="3"/>
-      <c r="C106" s="3"/>
-      <c r="D106" s="3"/>
-      <c r="E106" s="3"/>
-      <c r="F106" s="3"/>
-      <c r="G106" s="3"/>
+      <c r="B106" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="C106" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="D106" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E106" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F106" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G106" s="14">
+        <v>46009.554861111108</v>
+      </c>
       <c r="H106" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I106" s="3"/>
-      <c r="J106" s="3"/>
+      <c r="I106" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J106" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K106" s="3"/>
       <c r="L106" s="3"/>
       <c r="M106" s="3"/>
@@ -4160,21 +6122,37 @@
       <c r="V106" s="3"/>
       <c r="W106" s="3"/>
     </row>
-    <row r="107" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:23" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="B107" s="3"/>
-      <c r="C107" s="3"/>
-      <c r="D107" s="3"/>
-      <c r="E107" s="3"/>
-      <c r="F107" s="3"/>
-      <c r="G107" s="3"/>
+      <c r="B107" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="C107" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="D107" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E107" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F107" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G107" s="14">
+        <v>46009.556944444441</v>
+      </c>
       <c r="H107" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I107" s="3"/>
-      <c r="J107" s="3"/>
+      <c r="I107" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J107" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K107" s="3"/>
       <c r="L107" s="3"/>
       <c r="M107" s="3"/>
@@ -4189,21 +6167,37 @@
       <c r="V107" s="3"/>
       <c r="W107" s="3"/>
     </row>
-    <row r="108" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="B108" s="3"/>
-      <c r="C108" s="3"/>
-      <c r="D108" s="3"/>
-      <c r="E108" s="3"/>
-      <c r="F108" s="3"/>
-      <c r="G108" s="3"/>
+      <c r="B108" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="D108" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E108" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F108" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G108" s="14">
+        <v>46009.559027777781</v>
+      </c>
       <c r="H108" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I108" s="3"/>
-      <c r="J108" s="3"/>
+      <c r="I108" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J108" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K108" s="3"/>
       <c r="L108" s="3"/>
       <c r="M108" s="3"/>
@@ -4218,21 +6212,37 @@
       <c r="V108" s="3"/>
       <c r="W108" s="3"/>
     </row>
-    <row r="109" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B109" s="3"/>
-      <c r="C109" s="3"/>
-      <c r="D109" s="3"/>
-      <c r="E109" s="3"/>
-      <c r="F109" s="3"/>
-      <c r="G109" s="3"/>
+      <c r="B109" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="C109" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="D109" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E109" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F109" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G109" s="14">
+        <v>46009.560416666667</v>
+      </c>
       <c r="H109" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I109" s="3"/>
-      <c r="J109" s="3"/>
+      <c r="I109" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J109" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K109" s="3"/>
       <c r="L109" s="3"/>
       <c r="M109" s="3"/>
@@ -4247,17 +6257,37 @@
       <c r="V109" s="3"/>
       <c r="W109" s="3"/>
     </row>
-    <row r="110" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A110" s="10"/>
-      <c r="B110" s="3"/>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3"/>
-      <c r="E110" s="3"/>
-      <c r="F110" s="3"/>
-      <c r="G110" s="3"/>
-      <c r="H110" s="3"/>
-      <c r="I110" s="3"/>
-      <c r="J110" s="3"/>
+    <row r="110" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="B110" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="C110" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="D110" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E110" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F110" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G110" s="14">
+        <v>46009.5625</v>
+      </c>
+      <c r="H110" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="I110" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J110" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K110" s="3"/>
       <c r="L110" s="3"/>
       <c r="M110" s="3"/>
@@ -4272,17 +6302,37 @@
       <c r="V110" s="3"/>
       <c r="W110" s="3"/>
     </row>
-    <row r="111" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A111" s="3"/>
-      <c r="B111" s="3"/>
-      <c r="C111" s="3"/>
-      <c r="D111" s="3"/>
-      <c r="E111" s="3"/>
-      <c r="F111" s="3"/>
-      <c r="G111" s="3"/>
-      <c r="H111" s="3"/>
-      <c r="I111" s="3"/>
-      <c r="J111" s="3"/>
+    <row r="111" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="B111" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="C111" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="D111" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E111" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F111" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G111" s="14">
+        <v>46009.563888888886</v>
+      </c>
+      <c r="H111" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="I111" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J111" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K111" s="3"/>
       <c r="L111" s="3"/>
       <c r="M111" s="3"/>
@@ -4297,17 +6347,37 @@
       <c r="V111" s="3"/>
       <c r="W111" s="3"/>
     </row>
-    <row r="112" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A112" s="3"/>
-      <c r="B112" s="3"/>
-      <c r="C112" s="3"/>
-      <c r="D112" s="3"/>
-      <c r="E112" s="3"/>
-      <c r="F112" s="3"/>
-      <c r="G112" s="3"/>
-      <c r="H112" s="3"/>
-      <c r="I112" s="3"/>
-      <c r="J112" s="3"/>
+    <row r="112" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="B112" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="C112" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="D112" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E112" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F112" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G112" s="14">
+        <v>46009.565972222219</v>
+      </c>
+      <c r="H112" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="I112" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J112" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K112" s="3"/>
       <c r="L112" s="3"/>
       <c r="M112" s="3"/>
@@ -4322,17 +6392,37 @@
       <c r="V112" s="3"/>
       <c r="W112" s="3"/>
     </row>
-    <row r="113" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A113" s="3"/>
-      <c r="B113" s="3"/>
-      <c r="C113" s="3"/>
-      <c r="D113" s="3"/>
-      <c r="E113" s="3"/>
-      <c r="F113" s="3"/>
-      <c r="G113" s="3"/>
-      <c r="H113" s="3"/>
-      <c r="I113" s="3"/>
-      <c r="J113" s="3"/>
+    <row r="113" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="B113" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C113" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="D113" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E113" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F113" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G113" s="14">
+        <v>46009.567361111112</v>
+      </c>
+      <c r="H113" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="I113" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J113" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K113" s="3"/>
       <c r="L113" s="3"/>
       <c r="M113" s="3"/>
@@ -4347,17 +6437,37 @@
       <c r="V113" s="3"/>
       <c r="W113" s="3"/>
     </row>
-    <row r="114" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A114" s="3"/>
-      <c r="B114" s="3"/>
-      <c r="C114" s="3"/>
-      <c r="D114" s="3"/>
-      <c r="E114" s="3"/>
-      <c r="F114" s="3"/>
-      <c r="G114" s="3"/>
-      <c r="H114" s="3"/>
-      <c r="I114" s="3"/>
-      <c r="J114" s="3"/>
+    <row r="114" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="B114" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="C114" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="D114" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E114" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F114" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G114" s="14">
+        <v>46009.569444444445</v>
+      </c>
+      <c r="H114" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="I114" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J114" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K114" s="3"/>
       <c r="L114" s="3"/>
       <c r="M114" s="3"/>
@@ -4372,17 +6482,37 @@
       <c r="V114" s="3"/>
       <c r="W114" s="3"/>
     </row>
-    <row r="115" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A115" s="3"/>
-      <c r="B115" s="3"/>
-      <c r="C115" s="3"/>
-      <c r="D115" s="3"/>
-      <c r="E115" s="3"/>
-      <c r="F115" s="3"/>
-      <c r="G115" s="3"/>
-      <c r="H115" s="3"/>
-      <c r="I115" s="3"/>
-      <c r="J115" s="3"/>
+    <row r="115" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="B115" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="C115" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="D115" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E115" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F115" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G115" s="14">
+        <v>46009.570833333331</v>
+      </c>
+      <c r="H115" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="I115" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J115" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K115" s="3"/>
       <c r="L115" s="3"/>
       <c r="M115" s="3"/>
@@ -4397,17 +6527,37 @@
       <c r="V115" s="3"/>
       <c r="W115" s="3"/>
     </row>
-    <row r="116" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A116" s="3"/>
-      <c r="B116" s="3"/>
-      <c r="C116" s="3"/>
-      <c r="D116" s="3"/>
-      <c r="E116" s="3"/>
-      <c r="F116" s="3"/>
-      <c r="G116" s="3"/>
-      <c r="H116" s="3"/>
-      <c r="I116" s="3"/>
-      <c r="J116" s="3"/>
+    <row r="116" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="B116" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="C116" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="D116" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E116" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F116" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G116" s="14">
+        <v>46009.572916666664</v>
+      </c>
+      <c r="H116" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="I116" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J116" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K116" s="3"/>
       <c r="L116" s="3"/>
       <c r="M116" s="3"/>
@@ -4422,17 +6572,37 @@
       <c r="V116" s="3"/>
       <c r="W116" s="3"/>
     </row>
-    <row r="117" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A117" s="3"/>
-      <c r="B117" s="3"/>
-      <c r="C117" s="3"/>
-      <c r="D117" s="3"/>
-      <c r="E117" s="3"/>
-      <c r="F117" s="3"/>
-      <c r="G117" s="3"/>
-      <c r="H117" s="3"/>
-      <c r="I117" s="3"/>
-      <c r="J117" s="3"/>
+    <row r="117" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="B117" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="C117" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="D117" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E117" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F117" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G117" s="14">
+        <v>46009.574305555558</v>
+      </c>
+      <c r="H117" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="I117" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J117" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K117" s="3"/>
       <c r="L117" s="3"/>
       <c r="M117" s="3"/>
@@ -4447,17 +6617,37 @@
       <c r="V117" s="3"/>
       <c r="W117" s="3"/>
     </row>
-    <row r="118" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A118" s="3"/>
-      <c r="B118" s="3"/>
-      <c r="C118" s="3"/>
-      <c r="D118" s="3"/>
-      <c r="E118" s="3"/>
-      <c r="F118" s="3"/>
-      <c r="G118" s="3"/>
-      <c r="H118" s="3"/>
-      <c r="I118" s="3"/>
-      <c r="J118" s="3"/>
+    <row r="118" spans="1:23" ht="16.8" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A118" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="B118" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="C118" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="D118" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E118" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F118" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G118" s="14">
+        <v>46009.576388888891</v>
+      </c>
+      <c r="H118" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="I118" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J118" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K118" s="3"/>
       <c r="L118" s="3"/>
       <c r="M118" s="3"/>
@@ -4472,7 +6662,7 @@
       <c r="V118" s="3"/>
       <c r="W118" s="3"/>
     </row>
-    <row r="119" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.35">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -4480,7 +6670,7 @@
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
       <c r="G119" s="3"/>
-      <c r="H119" s="3"/>
+      <c r="H119" s="12"/>
       <c r="I119" s="3"/>
       <c r="J119" s="3"/>
       <c r="K119" s="3"/>
